--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAE6346-1C8A-4083-A416-9786A9A4A8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62B5974-9E73-457B-905F-7DA1D40EE2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -435,14 +435,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{68733429-A9FA-4187-B93D-3BEA15728D17}"/>
@@ -917,7 +916,7 @@
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1087,203 +1086,185 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="3">
-        <v>2021</v>
-      </c>
-      <c r="C1" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D1" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E1" s="3">
         <v>2024</v>
       </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
       <c r="F1">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="G1">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="H1">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="I1">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="J1">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="K1">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="L1">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="M1">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="N1">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="O1">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="P1">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="Q1">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="R1">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="S1">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="T1">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="U1">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="V1">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="W1">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="X1">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="Y1">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="Z1">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="AA1">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="AB1">
-        <v>2047</v>
-      </c>
-      <c r="AC1">
-        <v>2048</v>
-      </c>
-      <c r="AD1">
-        <v>2049</v>
-      </c>
-      <c r="AE1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="U2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="V2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="X2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AA2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AB2">
-        <v>0.6</v>
-      </c>
-      <c r="AC2">
-        <v>0.6</v>
-      </c>
-      <c r="AD2">
-        <v>0.6</v>
-      </c>
-      <c r="AE2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1368,17 +1349,8 @@
       <c r="AB3">
         <v>0.8</v>
       </c>
-      <c r="AC3">
-        <v>0.8</v>
-      </c>
-      <c r="AD3">
-        <v>0.8</v>
-      </c>
-      <c r="AE3">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1463,17 +1435,8 @@
       <c r="AB4">
         <v>0.8</v>
       </c>
-      <c r="AC4">
-        <v>0.8</v>
-      </c>
-      <c r="AD4">
-        <v>0.8</v>
-      </c>
-      <c r="AE4">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1558,17 +1521,8 @@
       <c r="AB5">
         <v>1</v>
       </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1653,17 +1607,8 @@
       <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1748,17 +1693,8 @@
       <c r="AB7">
         <v>1</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1843,17 +1779,8 @@
       <c r="AB8">
         <v>1</v>
       </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1938,17 +1865,8 @@
       <c r="AB9">
         <v>1</v>
       </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2033,17 +1951,8 @@
       <c r="AB10">
         <v>1</v>
       </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AD10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2128,17 +2037,8 @@
       <c r="AB11">
         <v>1</v>
       </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2223,17 +2123,8 @@
       <c r="AB12">
         <v>0.8</v>
       </c>
-      <c r="AC12">
-        <v>0.8</v>
-      </c>
-      <c r="AD12">
-        <v>0.8</v>
-      </c>
-      <c r="AE12">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2318,142 +2209,121 @@
       <c r="AB13">
         <v>0.8</v>
       </c>
-      <c r="AC13">
-        <v>0.8</v>
-      </c>
-      <c r="AD13">
-        <v>0.8</v>
-      </c>
-      <c r="AE13">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <f>B2</f>
-        <v>0.6</v>
+        <f t="shared" ref="B14:AB14" si="0">B2</f>
+        <v>0.8</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C2</f>
-        <v>0.6</v>
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="U14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="V14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="X14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AA14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AB14">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="AE14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2538,17 +2408,8 @@
       <c r="AB15">
         <v>1</v>
       </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>1</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2633,17 +2494,8 @@
       <c r="AB16">
         <v>0.8</v>
       </c>
-      <c r="AC16">
-        <v>0.8</v>
-      </c>
-      <c r="AD16">
-        <v>0.8</v>
-      </c>
-      <c r="AE16">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2728,17 +2580,8 @@
       <c r="AB17">
         <v>0.8</v>
       </c>
-      <c r="AC17">
-        <v>0.8</v>
-      </c>
-      <c r="AD17">
-        <v>0.8</v>
-      </c>
-      <c r="AE17">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2823,17 +2666,8 @@
       <c r="AB18">
         <v>0.8</v>
       </c>
-      <c r="AC18">
-        <v>0.8</v>
-      </c>
-      <c r="AD18">
-        <v>0.8</v>
-      </c>
-      <c r="AE18">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2918,17 +2752,8 @@
       <c r="AB19">
         <v>0.8</v>
       </c>
-      <c r="AC19">
-        <v>0.8</v>
-      </c>
-      <c r="AD19">
-        <v>0.8</v>
-      </c>
-      <c r="AE19">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3013,17 +2838,8 @@
       <c r="AB20">
         <v>0.8</v>
       </c>
-      <c r="AC20">
-        <v>0.8</v>
-      </c>
-      <c r="AD20">
-        <v>0.8</v>
-      </c>
-      <c r="AE20">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3108,17 +2924,8 @@
       <c r="AB21">
         <v>0.8</v>
       </c>
-      <c r="AC21">
-        <v>0.8</v>
-      </c>
-      <c r="AD21">
-        <v>0.8</v>
-      </c>
-      <c r="AE21">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3203,17 +3010,8 @@
       <c r="AB22">
         <v>0.8</v>
       </c>
-      <c r="AC22">
-        <v>0.8</v>
-      </c>
-      <c r="AD22">
-        <v>0.8</v>
-      </c>
-      <c r="AE22">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3298,17 +3096,8 @@
       <c r="AB23">
         <v>0.8</v>
       </c>
-      <c r="AC23">
-        <v>0.8</v>
-      </c>
-      <c r="AD23">
-        <v>0.8</v>
-      </c>
-      <c r="AE23">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -3393,17 +3182,8 @@
       <c r="AB24">
         <v>0.8</v>
       </c>
-      <c r="AC24">
-        <v>0.8</v>
-      </c>
-      <c r="AD24">
-        <v>0.8</v>
-      </c>
-      <c r="AE24">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -3486,15 +3266,6 @@
         <v>0.8</v>
       </c>
       <c r="AB25">
-        <v>0.8</v>
-      </c>
-      <c r="AC25">
-        <v>0.8</v>
-      </c>
-      <c r="AD25">
-        <v>0.8</v>
-      </c>
-      <c r="AE25">
         <v>0.8</v>
       </c>
     </row>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62B5974-9E73-457B-905F-7DA1D40EE2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A8C125-1BDA-4536-BA95-3365DBDBC4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
@@ -1186,82 +1186,82 @@
         <v>0.8</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="R2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="U2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="V2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="X2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Y2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AB2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">
@@ -2220,107 +2220,107 @@
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="U14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="V14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="X14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Y14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AB14">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A8C125-1BDA-4536-BA95-3365DBDBC4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEF56231-EADA-4732-BB01-4A7FD241C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="C2">
         <v>0.6</v>
@@ -1269,85 +1269,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.35">
@@ -1355,85 +1355,85 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">
@@ -2043,85 +2043,85 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
@@ -2129,85 +2129,85 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
@@ -2215,112 +2215,85 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <f t="shared" ref="B14:AB14" si="0">B2</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="U14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="V14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="X14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
@@ -2414,85 +2387,85 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.35">
@@ -2500,85 +2473,85 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB17">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.35">
@@ -2586,85 +2559,85 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.35">
@@ -2672,85 +2645,85 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB19">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
@@ -2758,85 +2731,85 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
@@ -2844,85 +2817,85 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB21">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
@@ -2930,85 +2903,85 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB22">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
@@ -3016,85 +2989,85 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB23">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
@@ -3102,85 +3075,85 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB24">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.35">
@@ -3188,85 +3161,85 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AB25">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEF56231-EADA-4732-BB01-4A7FD241C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E50EE-69EF-4CE0-850F-6979306B690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0.6</v>
@@ -2215,85 +2215,112 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.9</v>
+        <f>B2</f>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>0.9</v>
+        <f t="shared" ref="C14:AB14" si="0">C2</f>
+        <v>0.6</v>
       </c>
       <c r="D14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="E14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="F14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="G14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="H14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="I14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="J14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="K14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="L14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="M14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="N14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="O14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="P14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="Q14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="R14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="S14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="T14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="U14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="V14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="W14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="X14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="Y14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="Z14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="AA14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
       <c r="AB14">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E50EE-69EF-4CE0-850F-6979306B690D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77524CF2-2DC8-4D06-AD0C-C2822503911A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -467,6 +467,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -488,6 +491,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -1269,85 +1275,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.35">
@@ -1355,85 +1361,85 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">
@@ -2043,85 +2049,85 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
@@ -2129,85 +2135,85 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
@@ -2215,7 +2221,6 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <f>B2</f>
         <v>1</v>
       </c>
       <c r="C14">
@@ -2414,85 +2419,85 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.35">
@@ -2500,85 +2505,85 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB17">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.35">
@@ -2586,85 +2591,85 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB18">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.35">
@@ -2672,85 +2677,85 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
@@ -2758,85 +2763,85 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
@@ -2844,85 +2849,85 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
@@ -2930,85 +2935,85 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">
@@ -3016,85 +3021,85 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB23">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.35">
@@ -3102,85 +3107,85 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.35">
@@ -3188,85 +3193,85 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77524CF2-2DC8-4D06-AD0C-C2822503911A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6137096-4E85-42E0-82C2-987548C18D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
@@ -1275,85 +1275,85 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.35">
@@ -1361,85 +1361,85 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">
@@ -2049,85 +2049,85 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
@@ -2135,85 +2135,85 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
@@ -2677,85 +2677,85 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.35">
@@ -2763,85 +2763,85 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.35">
@@ -2849,85 +2849,85 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.35">
@@ -2935,85 +2935,85 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.35">

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9841894-88E4-4415-8A7E-DD2FE4CFDB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF73A49-FEDC-4BBB-BCB2-03B2ADBAAE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -601,9 +601,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -641,7 +641,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -747,7 +747,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -889,7 +889,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1092,185 +1092,179 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E1">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="F1">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G1">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="H1">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="I1">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="J1">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="K1">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="L1">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="M1">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="N1">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="O1">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="P1">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Q1">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="R1">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="S1">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="T1">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="U1">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="V1">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="W1">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="X1">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y1">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Z1">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AA1">
-        <v>2049</v>
-      </c>
-      <c r="AB1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.9</v>
+        <v>0.63</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="K2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="L2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="M2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="N2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="O2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="P2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="Q2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="R2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="S2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="T2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="U2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="V2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="W2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="X2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="Y2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="Z2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AA2">
-        <v>0.6</v>
-      </c>
-      <c r="AB2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1352,11 +1346,8 @@
       <c r="AA3">
         <v>0.9</v>
       </c>
-      <c r="AB3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1438,11 +1429,8 @@
       <c r="AA4">
         <v>0.9</v>
       </c>
-      <c r="AB4">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1524,11 +1512,8 @@
       <c r="AA5">
         <v>1</v>
       </c>
-      <c r="AB5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1610,11 +1595,8 @@
       <c r="AA6">
         <v>1</v>
       </c>
-      <c r="AB6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1696,11 +1678,8 @@
       <c r="AA7">
         <v>1</v>
       </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1782,11 +1761,8 @@
       <c r="AA8">
         <v>1</v>
       </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1868,11 +1844,8 @@
       <c r="AA9">
         <v>1</v>
       </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1954,11 +1927,8 @@
       <c r="AA10">
         <v>1</v>
       </c>
-      <c r="AB10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2040,11 +2010,8 @@
       <c r="AA11">
         <v>1</v>
       </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2126,11 +2093,8 @@
       <c r="AA12">
         <v>0.9</v>
       </c>
-      <c r="AB12">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2212,124 +2176,91 @@
       <c r="AA13">
         <v>0.9</v>
       </c>
-      <c r="AB13">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <f>B2</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AB14" si="0">C2</f>
         <v>0.6</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="U14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="V14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="X14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="AB14">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2411,11 +2342,8 @@
       <c r="AA15">
         <v>1</v>
       </c>
-      <c r="AB15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2497,11 +2425,8 @@
       <c r="AA16">
         <v>1</v>
       </c>
-      <c r="AB16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2583,11 +2508,8 @@
       <c r="AA17">
         <v>1</v>
       </c>
-      <c r="AB17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2669,11 +2591,8 @@
       <c r="AA18">
         <v>1</v>
       </c>
-      <c r="AB18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28">
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2755,11 +2674,8 @@
       <c r="AA19">
         <v>0.9</v>
       </c>
-      <c r="AB19">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28">
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2841,11 +2757,8 @@
       <c r="AA20">
         <v>0.9</v>
       </c>
-      <c r="AB20">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28">
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2927,11 +2840,8 @@
       <c r="AA21">
         <v>0.9</v>
       </c>
-      <c r="AB21">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -3013,11 +2923,8 @@
       <c r="AA22">
         <v>0.9</v>
       </c>
-      <c r="AB22">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3099,233 +3006,170 @@
       <c r="AA23">
         <v>1</v>
       </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28">
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
         <v>45</v>
       </c>
       <c r="B24">
-        <f>B13</f>
         <v>0.9</v>
       </c>
       <c r="C24">
-        <f t="shared" ref="C24:AB24" si="1">C13</f>
         <v>0.9</v>
       </c>
       <c r="D24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="E24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="F24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="G24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="H24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="I24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="J24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="K24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="L24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="M24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="N24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="P24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="R24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="S24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="T24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="U24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="V24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="W24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="X24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="Z24">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
-      <c r="AB24">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
         <v>46</v>
       </c>
       <c r="B25">
-        <f>B4</f>
         <v>0.9</v>
       </c>
       <c r="C25">
-        <f t="shared" ref="C25:AB25" si="2">C4</f>
         <v>0.9</v>
       </c>
       <c r="D25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="E25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="F25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="G25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="H25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="I25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="J25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="K25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="L25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="M25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="N25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="O25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="P25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="R25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="S25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="T25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="U25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="V25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="W25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="X25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="Z25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="AB25">
-        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
     </row>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\elec\RAF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-dev-sandbox\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF73A49-FEDC-4BBB-BCB2-03B2ADBAAE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0AEAB7-2D16-453A-B4D3-25ACC862D5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-23820" yWindow="3465" windowWidth="21600" windowHeight="12645" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -351,7 +351,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,9 +601,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -641,7 +641,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -747,7 +747,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -889,7 +889,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -898,27 +898,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
   <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,157 +926,157 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -1093,12 +1093,12 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2011,173 +2011,173 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA13">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3007,90 +3007,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>45</v>
       </c>
       <c r="B24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -3184,13 +3184,13 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-dev-sandbox\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0AEAB7-2D16-453A-B4D3-25ACC862D5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56CAB2-6239-4ED1-B74E-3A7D68FFCF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23820" yWindow="3465" windowWidth="21600" windowHeight="12645" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="2055" yWindow="3375" windowWidth="21600" windowHeight="12645" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Source:</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>Update 2026-08-18: natural gas peaker and petroleum RAF set to 0.8 (were 1.0 since 2026-08-17). SYSHECF for these sources calibrates to EIA CF / 0.8 so realized CFs are unchanged at observed EIA levels.</t>
   </si>
 </sst>
 </file>
@@ -897,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
@@ -1079,6 +1082,11 @@
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2016,82 +2024,82 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Y12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Z12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
@@ -2099,82 +2107,82 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Y13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
